--- a/order_forms/043_hospital_supply_delivery_form--order_forms.xlsx
+++ b/order_forms/043_hospital_supply_delivery_form--order_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="17" customWidth="1" min="2" max="2"/>
+    <col width="17" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'urgent',_'value':_1}</t>
+          <t>urgent</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Urgent', 'value': 1}</t>
+          <t>Urgent</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'non-urgent',_'value':_2}</t>
+          <t>non-urgent</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Non-Urgent', 'value': 2}</t>
+          <t>Non-Urgent</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'address_1',_'value':_'address_1'}</t>
+          <t>address_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Address 1', 'value': 'Address 1'}</t>
+          <t>Address 1</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'address_2',_'value':_'address_2'}</t>
+          <t>address_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Address 2', 'value': 'Address 2'}</t>
+          <t>Address 2</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'address_3',_'value':_'address_3'}</t>
+          <t>address_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Address 3', 'value': 'Address 3'}</t>
+          <t>Address 3</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'confirmed',_'value':_1}</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Confirmed', 'value': 1}</t>
+          <t>Confirmed</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_confirmed',_'value':_2}</t>
+          <t>not_confirmed</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not Confirmed', 'value': 2}</t>
+          <t>Not Confirmed</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'between_9am-5pm',_'value':_'9am-5pm'}</t>
+          <t>between_9am-5pm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Between 9am-5pm', 'value': '9am-5pm'}</t>
+          <t>Between 9am-5pm</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'after_5pm',_'value':_'after_5pm'}</t>
+          <t>after_5pm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'After 5pm', 'value': 'After 5pm'}</t>
+          <t>After 5pm</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'open',_'value':_1}</t>
+          <t>open</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Open', 'value': 1}</t>
+          <t>Open</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'closed',_'value':_2}</t>
+          <t>closed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Closed', 'value': 2}</t>
+          <t>Closed</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'confirmed',_'value':_1}</t>
+          <t>confirmed</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Confirmed', 'value': 1}</t>
+          <t>Confirmed</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'not_confirmed',_'value':_2}</t>
+          <t>not_confirmed</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Not Confirmed', 'value': 2}</t>
+          <t>Not Confirmed</t>
         </is>
       </c>
     </row>
